--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-03 18:33</t>
+          <t>ultimo controllo: 2026-06-03 18:42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Scores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validazione" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,52 +432,387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>4.9</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-03 18:42</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>three.ws</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.007389</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.33, buy_pressure:0.072</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Permission-less Lending</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>volume_accel:1.7, confluence_bonus:1.5, young_with_volume:1.275, buy_pressure:0.049</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>9UuLsJ3jf8ViBNeRcwXD53re5G3ypgfKK3s2EiMMpump</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Orizzonte</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Valore atteso NETTO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—ancora maturo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>72h</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—ancora maturo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>168h</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—ancora maturo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Score_entry</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Prezzo_entry</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ret_72h_netto</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Entrata</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>three</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.007389</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007389</v>
+        <v>0.007783</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.33, buy_pressure:0.072</t>
+          <t>volume_accel:1.57, biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.132</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="E3" t="n">
         <v>0.0008541999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>volume_accel:1.7, confluence_bonus:1.5, young_with_volume:1.275, buy_pressure:0.049</t>
+          <t>volume_accel:1.662, confluence_bonus:1.5, young_with_volume:1.246, buy_pressure:0.114</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007783</v>
+        <v>0.006709</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.57, biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.132</t>
+          <t>volume_accel:1.8, biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.201</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.52</v>
+        <v>4.31</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0007179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>volume_accel:1.662, confluence_bonus:1.5, young_with_volume:1.246, buy_pressure:0.114</t>
+          <t>volume_accel:1.539, confluence_bonus:1.5, young_with_volume:1.154, buy_pressure:0.12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>6.21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006709</v>
+        <v>0.00622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.8, biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.201</t>
+          <t>biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.48, buy_pressure:0.231</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.31</v>
+        <v>4.08</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007179</v>
+        <v>0.0006395</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>volume_accel:1.539, confluence_bonus:1.5, young_with_volume:1.154, buy_pressure:0.12</t>
+          <t>confluence_bonus:1.5, volume_accel:1.381, young_with_volume:1.035, buy_pressure:0.163</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -436,8 +436,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,27 +525,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>three</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>three.ws</t>
+          <t>HelloKittyRPGKickflip360</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.21</v>
+        <v>5.21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00622</v>
+        <v>0.0001873</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biz_mentions:1.5, young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.48, buy_pressure:0.231</t>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.214</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,45 +554,45 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>geckoterminal_trending</t>
+          <t>dexscreener_boosts</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
+          <t>5GbhDpdSdE693wi3huTbjc9TtSXoKKQgezAt3e24pump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Permission-less Lending</t>
+          <t>three.ws</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.08</v>
+        <v>5.02</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006395</v>
+        <v>0.01128</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, volume_accel:1.381, young_with_volume:1.035, buy_pressure:0.163</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.185, volume_accel:1.169, biz_mentions:0.75, buy_pressure:0.42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -613,7 +613,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>9UuLsJ3jf8ViBNeRcwXD53re5G3ypgfKK3s2EiMMpump</t>
+          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -763,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,33 +784,61 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>5.9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001873</v>
+        <v>0.0002449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.214</t>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.328</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -588,11 +588,11 @@
         <v>5.02</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01128</v>
+        <v>0.01083</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.185, volume_accel:1.169, biz_mentions:0.75, buy_pressure:0.42</t>
+          <t>young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.1, biz_mentions:0.75, buy_pressure:0.172</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>16.4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.33</v>
+        <v>4.73</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002449</v>
+        <v>0.000174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.328</t>
+          <t>volume_accel:1.728, confluence_bonus:1.5, young_with_volume:1.296, buy_pressure:0.205</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.02</v>
+        <v>4.56</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01083</v>
+        <v>0.01167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.1, biz_mentions:0.75, buy_pressure:0.172</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.296, volume_accel:0.95, biz_mentions:0.499, buy_pressure:0.316</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>16.4</v>
+        <v>19.7</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000174</v>
+        <v>0.0001659</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.728, confluence_bonus:1.5, young_with_volume:1.296, buy_pressure:0.205</t>
+          <t>volume_accel:1.712, confluence_bonus:1.5, young_with_volume:1.284, buy_pressure:0.204</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01167</v>
+        <v>0.01236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.296, volume_accel:0.95, biz_mentions:0.499, buy_pressure:0.316</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.284, volume_accel:0.942, biz_mentions:0.499, buy_pressure:0.314</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001659</v>
+        <v>0.0001875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.712, confluence_bonus:1.5, young_with_volume:1.284, buy_pressure:0.204</t>
+          <t>volume_accel:1.664, confluence_bonus:1.5, young_with_volume:1.248, buy_pressure:0.207</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01236</v>
+        <v>0.01341</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.284, volume_accel:0.942, biz_mentions:0.499, buy_pressure:0.314</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.248, volume_accel:0.915, biz_mentions:0.499, buy_pressure:0.39</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19.9</v>
+        <v>20.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001875</v>
+        <v>0.0002072</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.664, confluence_bonus:1.5, young_with_volume:1.248, buy_pressure:0.207</t>
+          <t>volume_accel:1.605, confluence_bonus:1.5, young_with_volume:1.204, buy_pressure:0.187</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01341</v>
+        <v>0.01194</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.248, volume_accel:0.915, biz_mentions:0.499, buy_pressure:0.39</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.204, volume_accel:0.883, biz_mentions:0.499, buy_pressure:0.243</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,27 +525,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HelloKittyRPGKickflip360</t>
+          <t>three.ws</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002072</v>
+        <v>0.008481000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.605, confluence_bonus:1.5, young_with_volume:1.204, buy_pressure:0.187</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.031, volume_accel:0.756, biz_mentions:0.75, buy_pressure:0.289</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,45 +554,45 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.699999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dexscreener_boosts</t>
+          <t>geckoterminal_trending</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5GbhDpdSdE693wi3huTbjc9TtSXoKKQgezAt3e24pump</t>
+          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>three</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>three.ws</t>
+          <t>HelloKittyRPGKickflip360</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.33</v>
+        <v>4.07</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01194</v>
+        <v>0.0001861</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.204, volume_accel:0.883, biz_mentions:0.499, buy_pressure:0.243</t>
+          <t>confluence_bonus:1.5, volume_accel:1.375, young_with_volume:1.031, buy_pressure:0.165</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,19 +601,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>21.2</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>geckoterminal_trending</t>
+          <t>dexscreener_boosts</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
+          <t>5GbhDpdSdE693wi3huTbjc9TtSXoKKQgezAt3e24pump</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,188 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>three</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>three.ws</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.008481000000000001</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.031, volume_accel:0.756, biz_mentions:0.75, buy_pressure:0.289</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RPGKITTY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HelloKittyRPGKickflip360</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0001861</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, volume_accel:1.375, young_with_volume:1.031, buy_pressure:0.165</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>5GbhDpdSdE693wi3huTbjc9TtSXoKKQgezAt3e24pump</t>
+          <t>ultimo controllo: 2026-06-04 19:30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -640,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -729,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-04 19:30</t>
+          <t>ultimo controllo: 2026-06-04 21:54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>—ancora maturo</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-04 21:54</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>three.ws</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.006728</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>confluence_bonus:1.5, biz_mentions:1.249, young_with_volume:0.602, volume_accel:0.441, buy_pressure:0.319</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
         </is>
       </c>
     </row>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,141 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>three</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>three.ws</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.006728</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, biz_mentions:1.249, young_with_volume:0.602, volume_accel:0.441, buy_pressure:0.319</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>FeMbDoX7R1Psc4GEcvJdsbNbZA3bfztcyDCatJVJpump</t>
+          <t>ultimo controllo: 2026-06-05 04:46</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -593,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -682,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-05 04:46</t>
+          <t>ultimo controllo: 2026-06-05 08:54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-5.69%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-05 08:54</t>
+          <t>ultimo controllo: 2026-06-05 12:21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-05 12:21</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>Everyone is lying to you for $</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.001006</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.456</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CotmxNNE85WeyFr5xvzJksEZhLctqhD9uzFFbkHCpump</t>
         </is>
       </c>
     </row>
@@ -487,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -622,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,33 +765,61 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>5.9</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001006</v>
+        <v>0.0006766</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.456</t>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.414</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -436,8 +436,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,27 +525,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Everyone is lying to you for $</t>
+          <t>Golden Goal</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.16</v>
+        <v>5.29</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006766</v>
+        <v>0.000203</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.414</t>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.291</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CotmxNNE85WeyFr5xvzJksEZhLctqhD9uzFFbkHCpump</t>
+          <t>GU527smM71ht8aCA8ouShfXhahVq6crz51FMbfZ8pump</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -716,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,33 +793,61 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>5.9</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.29</v>
+        <v>5.11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000203</v>
+        <v>0.0002149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.291</t>
+          <t>volume_accel:1.874, confluence_bonus:1.5, young_with_volume:1.406, buy_pressure:0.333</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.11</v>
+        <v>4.82</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002149</v>
+        <v>0.0002238</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.874, confluence_bonus:1.5, young_with_volume:1.406, buy_pressure:0.333</t>
+          <t>volume_accel:1.718, confluence_bonus:1.5, young_with_volume:1.289, buy_pressure:0.31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>1.9</v>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.82</v>
+        <v>4.26</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002238</v>
+        <v>0.0002002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.718, confluence_bonus:1.5, young_with_volume:1.289, buy_pressure:0.31</t>
+          <t>confluence_bonus:1.5, volume_accel:1.322, young_with_volume:0.991, buy_pressure:0.444</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,141 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Golden Goal</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0002002</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, volume_accel:1.322, young_with_volume:0.991, buy_pressure:0.444</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>GU527smM71ht8aCA8ouShfXhahVq6crz51FMbfZ8pump</t>
+          <t>ultimo controllo: 2026-06-06 08:04</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -593,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -682,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 08:04</t>
+          <t>ultimo controllo: 2026-06-06 10:19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 10:19</t>
+          <t>ultimo controllo: 2026-06-06 12:16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 12:16</t>
+          <t>ultimo controllo: 2026-06-06 14:53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 14:53</t>
+          <t>ultimo controllo: 2026-06-06 16:18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>-11.76%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 16:18</t>
+          <t>ultimo controllo: 2026-06-06 18:20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 18:20</t>
+          <t>ultimo controllo: 2026-06-06 20:20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>—ancora maturo</t>
+          <t>-36.87%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-35.09%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.65%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 20:20</t>
+          <t>ultimo controllo: 2026-06-06 22:15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-11.76%</t>
+          <t>-15.16%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-06 22:15</t>
+          <t>ultimo controllo: 2026-06-07 00:19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-07 00:19</t>
+          <t>ultimo controllo: 2026-06-07 05:51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,11 +554,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-36.87%</t>
+          <t>-34.08%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>4.3</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-07 05:51</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>Bountywork</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.000678</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.169</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>J4x1EMmQjF6WEzXq2tUtzY89x5aMhYz5CzfevcJEpump</t>
         </is>
       </c>
     </row>
@@ -487,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -622,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,25 +765,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -699,25 +793,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -727,33 +821,61 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>5.9</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.17</v>
+        <v>4.87</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000678</v>
+        <v>0.0006408</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.169</t>
+          <t>volume_accel:1.64, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.225</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -567,6 +567,53 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>J4x1EMmQjF6WEzXq2tUtzY89x5aMhYz5CzfevcJEpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Permission-less Lending</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0008887</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, confluence_bonus:1.5, liquidity_growth:0.6, buy_pressure:0.011</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>9UuLsJ3jf8ViBNeRcwXD53re5G3ypgfKK3s2EiMMpump</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.87</v>
+        <v>4.3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006408</v>
+        <v>0.0006584</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.64, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.225</t>
+          <t>young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.24, buy_pressure:0.057</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -567,53 +567,6 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>J4x1EMmQjF6WEzXq2tUtzY89x5aMhYz5CzfevcJEpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Magpie</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Permission-less Lending</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0008887</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>volume_accel:2.0, confluence_bonus:1.5, liquidity_growth:0.6, buy_pressure:0.011</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>9UuLsJ3jf8ViBNeRcwXD53re5G3ypgfKK3s2EiMMpump</t>
         </is>
       </c>
     </row>
@@ -628,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -763,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -812,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -840,25 +793,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -868,25 +821,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -896,33 +849,61 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>5.9</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -525,46 +525,93 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>BOUTYWORK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BOUTYWORK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0004491</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:1.799, confluence_bonus:1.5, young_with_volume:1.349, buy_pressure:0.112</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3oL99tu2qnxka3HnxY8g1cXNpgBJ5ojoSWWFiDMopump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Bountywork</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bountywork</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0006584</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.24, buy_pressure:0.057</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0008806</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>confluence_bonus:1.5, young_with_volume:1.349, volume_accel:1.115, buy_pressure:0.082</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>solana</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="H3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>geckoterminal_trending</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>J4x1EMmQjF6WEzXq2tUtzY89x5aMhYz5CzfevcJEpump</t>
         </is>
@@ -581,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -716,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +784,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +812,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +840,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,25 +868,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -849,25 +896,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -877,33 +924,61 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>5.9</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,39 +525,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BOUTYWORK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BOUTYWORK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0003805</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:1.666, confluence_bonus:1.5, young_with_volume:1.25, buy_pressure:0.144</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BOUTYWORK</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BOUTYWORK</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0004491</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>volume_accel:1.799, confluence_bonus:1.5, young_with_volume:1.349, buy_pressure:0.112</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.5</v>
-      </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -567,53 +567,6 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>3oL99tu2qnxka3HnxY8g1cXNpgBJ5ojoSWWFiDMopump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bountywork</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bountywork</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0008806</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.349, volume_accel:1.115, buy_pressure:0.082</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>J4x1EMmQjF6WEzXq2tUtzY89x5aMhYz5CzfevcJEpump</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.56</v>
+        <v>4.25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003805</v>
+        <v>0.0005951</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.666, confluence_bonus:1.5, young_with_volume:1.25, buy_pressure:0.144</t>
+          <t>confluence_bonus:1.5, volume_accel:1.492, young_with_volume:1.119, buy_pressure:0.141</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,141 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0005951</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, volume_accel:1.492, young_with_volume:1.119, buy_pressure:0.141</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>3oL99tu2qnxka3HnxY8g1cXNpgBJ5ojoSWWFiDMopump</t>
+          <t>ultimo controllo: 2026-06-07 22:17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -593,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -682,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-07 22:17</t>
+          <t>ultimo controllo: 2026-06-08 00:20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-08 00:20</t>
+          <t>ultimo controllo: 2026-06-08 06:05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-08 06:05</t>
+          <t>ultimo controllo: 2026-06-08 11:20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-15.16%</t>
+          <t>+11.16%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>4.2</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-08 11:20</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>PumpGO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0004694</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.028</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CujZ5W6GWYb5XYe3hsTJ6kjiaw5MdZjbKQEuGA6jpump</t>
         </is>
       </c>
     </row>
@@ -487,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -534,16 +628,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.16%</t>
+          <t>-3.00%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -554,11 +648,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-34.08%</t>
+          <t>-47.76%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -622,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,25 +849,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -783,25 +877,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -811,33 +905,61 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>5.9</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,46 +525,93 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>GOKU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Son Goku</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.001917</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:1.347</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BUvuChjfCJxfUyCRMNWtm2W5ygTc7vV7mK4N22tGpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>PumpGO</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0004694</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.028</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D3" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0006538</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, liquidity_growth:0.65, buy_pressure:0.132</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>solana</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="H3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>geckoterminal_trending</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>CujZ5W6GWYb5XYe3hsTJ6kjiaw5MdZjbKQEuGA6jpump</t>
         </is>
@@ -581,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -628,16 +675,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.00%</t>
+          <t>-4.73%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -716,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +784,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +812,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +840,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +868,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,25 +896,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -877,25 +924,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -905,25 +952,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -933,33 +980,61 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>5.9</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.35</v>
+        <v>5.89</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001917</v>
+        <v>0.001525</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:1.347</t>
+          <t>volume_accel:1.797, confluence_bonus:1.5, young_with_volume:1.348, buy_pressure:1.243</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.78</v>
+        <v>5.71</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006538</v>
+        <v>0.0004953</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, liquidity_growth:0.65, buy_pressure:0.132</t>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, liquidity_growth:0.584, buy_pressure:0.13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -695,11 +695,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-47.76%</t>
+          <t>-43.88%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.89</v>
+        <v>5.66</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001525</v>
+        <v>0.001477</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.797, confluence_bonus:1.5, young_with_volume:1.348, buy_pressure:1.243</t>
+          <t>volume_accel:1.679, confluence_bonus:1.5, young_with_volume:1.259, buy_pressure:1.224</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.71</v>
+        <v>5.42</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004953</v>
+        <v>0.0003877</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, liquidity_growth:0.584, buy_pressure:0.13</t>
+          <t>volume_accel:1.882, confluence_bonus:1.5, young_with_volume:1.411, liquidity_growth:0.546, buy_pressure:0.082</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.66</v>
+        <v>4.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001477</v>
+        <v>0.001358</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.679, confluence_bonus:1.5, young_with_volume:1.259, buy_pressure:1.224</t>
+          <t>confluence_bonus:1.5, volume_accel:1.267, buy_pressure:1.186, young_with_volume:0.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.42</v>
+        <v>4.52</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003877</v>
+        <v>0.0003685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>volume_accel:1.882, confluence_bonus:1.5, young_with_volume:1.411, liquidity_growth:0.546, buy_pressure:0.082</t>
+          <t>confluence_bonus:1.5, volume_accel:1.47, young_with_volume:1.102, liquidity_growth:0.412, buy_pressure:0.033</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>12.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,6 +614,53 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>CujZ5W6GWYb5XYe3hsTJ6kjiaw5MdZjbKQEuGA6jpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bankcoin</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0001912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.397</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2jCt3hj9vd7YpV7Sr3VA5nk3tdSpJtZezeoJXW4Xpump</t>
         </is>
       </c>
     </row>
@@ -628,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -763,14 +810,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,21 +831,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -812,21 +859,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -840,21 +887,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -868,21 +915,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -896,25 +943,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -924,25 +971,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -952,25 +999,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -980,25 +1027,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1008,33 +1055,61 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>5.9</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,11 +432,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -525,27 +525,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001358</v>
+        <v>0.003622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, volume_accel:1.267, buy_pressure:1.186, young_with_volume:0.95</t>
+          <t>young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.14, buy_pressure:0.112</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,45 +554,45 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dexscreener_boosts</t>
+          <t>geckoterminal_trending</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BUvuChjfCJxfUyCRMNWtm2W5ygTc7vV7mK4N22tGpump</t>
+          <t>BcHEaaTCvycPwwsJ9yQTXdHP9X2gCLkznDbZ8VySpump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PumpGO</t>
+          <t>Son Goku</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.52</v>
+        <v>4.17</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003685</v>
+        <v>0.001456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, volume_accel:1.47, young_with_volume:1.102, liquidity_growth:0.412, buy_pressure:0.033</t>
+          <t>confluence_bonus:1.5, volume_accel:0.979, buy_pressure:0.96, young_with_volume:0.734</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,66 +601,113 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>geckoterminal_trending</t>
+          <t>dexscreener_boosts</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CujZ5W6GWYb5XYe3hsTJ6kjiaw5MdZjbKQEuGA6jpump</t>
+          <t>BUvuChjfCJxfUyCRMNWtm2W5ygTc7vV7mK4N22tGpump</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bankcoin</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0002108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.325</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="I4" t="n">
         <v>3.5</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bankcoin</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0001912</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.397</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2jCt3hj9vd7YpV7Sr3VA5nk3tdSpJtZezeoJXW4Xpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PumpGO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0003261</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>confluence_bonus:1.5, volume_accel:1.182, young_with_volume:0.887, liquidity_growth:0.318, buy_pressure:0.168</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>solana</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2jCt3hj9vd7YpV7Sr3VA5nk3tdSpJtZezeoJXW4Xpump</t>
+      <c r="H5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CujZ5W6GWYb5XYe3hsTJ6kjiaw5MdZjbKQEuGA6jpump</t>
         </is>
       </c>
     </row>
@@ -675,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -810,14 +857,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -831,21 +878,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -859,21 +906,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -887,21 +934,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -915,21 +962,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -943,21 +990,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -971,25 +1018,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -999,25 +1046,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1027,25 +1074,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1055,25 +1102,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1083,33 +1130,61 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
         <v>5.9</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C20" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -541,11 +541,11 @@
         <v>4.25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003622</v>
+        <v>0.004112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>young_with_volume:1.5, confluence_bonus:1.5, volume_accel:1.14, buy_pressure:0.112</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.475, volume_accel:1.121, buy_pressure:0.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001456</v>
+        <v>0.001425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, volume_accel:0.979, buy_pressure:0.96, young_with_volume:0.734</t>
+          <t>confluence_bonus:1.5, volume_accel:0.946, buy_pressure:0.944, young_with_volume:0.71</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -632,14 +632,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002108</v>
+        <v>0.0002049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.325</t>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.317</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>84.8</v>
+        <v>85.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -661,53 +661,6 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>2jCt3hj9vd7YpV7Sr3VA5nk3tdSpJtZezeoJXW4Xpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PumpGO</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0003261</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, volume_accel:1.182, young_with_volume:0.887, liquidity_growth:0.318, buy_pressure:0.168</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>CujZ5W6GWYb5XYe3hsTJ6kjiaw5MdZjbKQEuGA6jpump</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004112</v>
+        <v>0.005091</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.475, volume_accel:1.121, buy_pressure:0.15</t>
+          <t>confluence_bonus:1.5, young_with_volume:1.446, volume_accel:1.099, buy_pressure:0.169</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="n">
         <v>3.1</v>
@@ -576,23 +576,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Bankcoin</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001425</v>
+        <v>0.0002019</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>confluence_bonus:1.5, volume_accel:0.946, buy_pressure:0.944, young_with_volume:0.71</t>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.307</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
@@ -612,53 +612,6 @@
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>BUvuChjfCJxfUyCRMNWtm2W5ygTc7vV7mK4N22tGpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bankcoin</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0002049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.317</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>2jCt3hj9vd7YpV7Sr3VA5nk3tdSpJtZezeoJXW4Xpump</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,188 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jotchua</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.005091</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, young_with_volume:1.446, volume_accel:1.099, buy_pressure:0.169</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>geckoterminal_trending</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>BcHEaaTCvycPwwsJ9yQTXdHP9X2gCLkznDbZ8VySpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bankcoin</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0002019</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.307</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2jCt3hj9vd7YpV7Sr3VA5nk3tdSpJtZezeoJXW4Xpump</t>
+          <t>ultimo controllo: 2026-06-09 12:16</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -640,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -729,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-09 12:16</t>
+          <t>ultimo controllo: 2026-06-09 14:25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-09 14:25</t>
+          <t>ultimo controllo: 2026-06-09 14:57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -839,25 +839,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -867,25 +867,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -895,25 +895,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -923,33 +923,61 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>5.9</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-09 14:57</t>
+          <t>ultimo controllo: 2026-06-09 18:19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.73%</t>
+          <t>-7.53%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>22%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-09 18:19</t>
+          <t>ultimo controllo: 2026-06-09 21:57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-7.53%</t>
+          <t>-9.34%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>3.7</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-09 21:57</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>XRP SUPERCYCLE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.001083</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, confluence_bonus:1.5, liquidity_growth:0.5, biz_mentions:0.25, buy_pressure:0.199</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7XLu71Wvq7zuNU7TP5qjYY8kqg9zxtrsb7sJEEF6pump</t>
         </is>
       </c>
     </row>
@@ -487,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -622,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003622</v>
+        <v>0.001083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001061</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001917</v>
+        <v>0.003622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0004694</v>
+        <v>0.001061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.57</v>
+        <v>6.35</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0002168</v>
+        <v>0.001917</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +877,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5</v>
+        <v>5.03</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004829</v>
+        <v>0.0004694</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.17</v>
+        <v>3.57</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000678</v>
+        <v>0.0002168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,25 +933,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="C17" t="n">
-        <v>0.000203</v>
+        <v>0.0004829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -867,25 +961,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.21</v>
+        <v>5.17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001006</v>
+        <v>0.000678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -895,25 +989,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.21</v>
+        <v>5.29</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001873</v>
+        <v>0.000203</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -923,25 +1017,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.001006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -951,33 +1045,89 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B23" t="n">
         <v>5.9</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C23" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,141 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>XRP SUPERCYCLE</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.001083</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>volume_accel:2.0, confluence_bonus:1.5, liquidity_growth:0.5, biz_mentions:0.25, buy_pressure:0.199</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>7XLu71Wvq7zuNU7TP5qjYY8kqg9zxtrsb7sJEEF6pump</t>
+          <t>ultimo controllo: 2026-06-10 04:42</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -593,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -628,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-9.34%</t>
+          <t>-9.42%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>18%</t>
         </is>
       </c>
     </row>
@@ -682,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 04:42</t>
+          <t>ultimo controllo: 2026-06-10 08:13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-9.42%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001105760034287844</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001083</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003622</v>
+        <v>0.001083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001061</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001917</v>
+        <v>0.003622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004694</v>
+        <v>0.001061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.57</v>
+        <v>6.35</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0002168</v>
+        <v>0.001917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.5</v>
+        <v>5.03</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0004829</v>
+        <v>0.0004694</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.17</v>
+        <v>3.57</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000678</v>
+        <v>0.0002168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,25 +895,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000203</v>
+        <v>0.0004829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -923,25 +923,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.21</v>
+        <v>5.17</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001006</v>
+        <v>0.000678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -951,25 +951,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.21</v>
+        <v>5.29</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001873</v>
+        <v>0.000203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -979,25 +979,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.001006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1007,33 +1007,89 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B25" t="n">
         <v>5.9</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C25" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 08:13</t>
+          <t>ultimo controllo: 2026-06-10 08:42</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -678,14 +678,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C13" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C20" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,25 +951,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -979,25 +979,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1007,25 +1007,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1035,25 +1035,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1063,33 +1063,61 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" t="n">
         <v>5.9</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C26" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 08:42</t>
+          <t>ultimo controllo: 2026-06-10 10:19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-43.88%</t>
+          <t>-27.18%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002135704384091754</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001105760034287844</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001083</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003622</v>
+        <v>0.001083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001061</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001917</v>
+        <v>0.003622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004694</v>
+        <v>0.001061</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.57</v>
+        <v>6.35</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0002168</v>
+        <v>0.001917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.5</v>
+        <v>5.03</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0004829</v>
+        <v>0.0004694</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.17</v>
+        <v>3.57</v>
       </c>
       <c r="C21" t="n">
-        <v>0.000678</v>
+        <v>0.0002168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,25 +979,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="C22" t="n">
-        <v>0.000203</v>
+        <v>0.0004829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1007,25 +1007,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.21</v>
+        <v>5.17</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001006</v>
+        <v>0.000678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1035,25 +1035,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.21</v>
+        <v>5.29</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0001873</v>
+        <v>0.000203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1063,25 +1063,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.001006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1091,33 +1091,89 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B28" t="n">
         <v>5.9</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C28" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 10:19</t>
+          <t>ultimo controllo: 2026-06-10 13:07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002135704384091754</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001105760034287844</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001083</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003622</v>
+        <v>0.001083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001061</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001917</v>
+        <v>0.003622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0004694</v>
+        <v>0.001061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.57</v>
+        <v>6.35</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0002168</v>
+        <v>0.001917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.5</v>
+        <v>5.03</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0004829</v>
+        <v>0.0004694</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,25 +1007,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.17</v>
+        <v>3.57</v>
       </c>
       <c r="C23" t="n">
-        <v>0.000678</v>
+        <v>0.0002168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1035,25 +1035,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="C24" t="n">
-        <v>0.000203</v>
+        <v>0.0004829</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1063,25 +1063,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.21</v>
+        <v>5.17</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001006</v>
+        <v>0.000678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1091,25 +1091,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.21</v>
+        <v>5.29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0001873</v>
+        <v>0.000203</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.001006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1147,33 +1147,89 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B30" t="n">
         <v>5.9</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C30" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 13:07</t>
+          <t>ultimo controllo: 2026-06-10 16:03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-27.18%</t>
+          <t>-37.38%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002135704384091754</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001105760034287844</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001083</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003622</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.39</v>
+        <v>4.45</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001061</v>
+        <v>0.001083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001917</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.03</v>
+        <v>4.25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0004694</v>
+        <v>0.003622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.57</v>
+        <v>3.39</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0002168</v>
+        <v>0.001061</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.5</v>
+        <v>6.35</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0004829</v>
+        <v>0.001917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,25 +1063,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.17</v>
+        <v>5.03</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000678</v>
+        <v>0.0004694</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1091,25 +1091,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.29</v>
+        <v>3.57</v>
       </c>
       <c r="C26" t="n">
-        <v>0.000203</v>
+        <v>0.0002168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.21</v>
+        <v>3.5</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001006</v>
+        <v>0.0004829</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1147,25 +1147,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.21</v>
+        <v>5.17</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0001873</v>
+        <v>0.000678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,25 +1175,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.53</v>
+        <v>5.29</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.000203</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1203,33 +1203,117 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>MONEY</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.001006</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-88.80%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>06-05 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>5.9</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C33" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 16:03</t>
+          <t>ultimo controllo: 2026-06-10 18:50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-37.38%</t>
+          <t>-32.65%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -678,14 +678,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C21" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1147,25 +1147,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,25 +1175,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1203,25 +1203,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1259,25 +1259,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1287,33 +1287,61 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B34" t="n">
         <v>5.9</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 18:50</t>
+          <t>ultimo controllo: 2026-06-10 18:56</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 18:56</t>
+          <t>ultimo controllo: 2026-06-10 20:46</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—ancora maturo</t>
+          <t>-59.97%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001180509886463268</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -734,14 +734,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -790,14 +790,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -846,14 +846,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -930,14 +930,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C22" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1147,25 +1147,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,25 +1175,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1203,25 +1203,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C30" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1259,25 +1259,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1287,25 +1287,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1315,33 +1315,61 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" t="n">
         <v>5.9</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C35" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 20:46</t>
+          <t>ultimo controllo: 2026-06-10 22:18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001180509886463268</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -734,14 +734,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -874,14 +874,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -958,14 +958,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C23" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1175,25 +1175,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1203,25 +1203,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C31" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1259,25 +1259,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1287,25 +1287,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1315,61 +1315,89 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B36" t="n">
         <v>5.9</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>4.4</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-10 22:18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>Hachiko</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0001014</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.286</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>solana</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EykG1EFLxGkWAYjrfiF7Pysoj6xje6wkSf8qPLFapump</t>
         </is>
       </c>
     </row>
@@ -487,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -534,16 +628,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -622,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C9" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001180509886463268</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -762,14 +856,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -790,14 +884,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -846,14 +940,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +961,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -902,14 +996,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -986,14 +1080,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1101,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1129,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C24" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1175,25 +1269,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1203,25 +1297,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1231,25 +1325,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C31" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1259,25 +1353,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C32" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1287,25 +1381,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1315,25 +1409,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1343,61 +1437,89 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B37" t="n">
         <v>5.9</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.29</v>
+        <v>4.25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001014</v>
+        <v>9.682e-05</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:2.0, young_with_volume:1.5, confluence_bonus:1.5, buy_pressure:0.286</t>
+          <t>confluence_bonus:1.5, volume_accel:1.497, young_with_volume:1.123, buy_pressure:0.135</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-19.86%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
@@ -668,11 +668,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-59.97%</t>
+          <t>-74.15%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -716,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001014</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C10" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001180509886463268</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -884,14 +884,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -912,14 +912,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -968,14 +968,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +1073,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1108,14 +1108,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C25" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1297,25 +1297,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1325,25 +1325,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1353,25 +1353,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C32" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1381,25 +1381,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C33" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1409,25 +1409,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1437,25 +1437,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1465,25 +1465,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1493,33 +1493,61 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B38" t="n">
         <v>5.9</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,141 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hachiko</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.682e-05</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>confluence_bonus:1.5, volume_accel:1.497, young_with_volume:1.123, buy_pressure:0.135</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>solana</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>EykG1EFLxGkWAYjrfiF7Pysoj6xje6wkSf8qPLFapump</t>
+          <t>ultimo controllo: 2026-06-11 16:23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -581,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -593,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -628,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-19.86%</t>
+          <t>-9.25%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -648,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-32.65%</t>
+          <t>-39.39%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>22%</t>
         </is>
       </c>
     </row>
@@ -682,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -716,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001014</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001180509886463268</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -877,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C16" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -933,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -961,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -989,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1017,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002135704384091754</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1101,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1129,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001083</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.003622</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001061</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1175,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001917</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1297,21 +1203,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0004694</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1325,25 +1231,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.57</v>
+        <v>4.45</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0002168</v>
+        <v>0.001083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1353,25 +1259,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0004829</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1381,25 +1287,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.17</v>
+        <v>4.25</v>
       </c>
       <c r="C33" t="n">
-        <v>0.000678</v>
+        <v>0.003622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1409,25 +1315,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5.29</v>
+        <v>3.39</v>
       </c>
       <c r="C34" t="n">
-        <v>0.000203</v>
+        <v>0.001061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1437,25 +1343,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.21</v>
+        <v>6.35</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001006</v>
+        <v>0.001917</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1465,89 +1371,257 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5.21</v>
+        <v>5.03</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001873</v>
+        <v>0.0004694</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0002168</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>BOUTYWORK</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0004829</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-98.63%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>06-07 14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bountywork</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.000678</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>+56.33%</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>06-07 09:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GOLDENGOAL</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.000203</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-28.34%</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>06-05 20:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MONEY</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001006</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-88.80%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>06-05 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B44" t="n">
         <v>5.9</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C44" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-11 16:23</t>
+          <t>ultimo controllo: 2026-06-11 20:38</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-9.25%</t>
+          <t>-13.38%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-39.39%</t>
+          <t>-37.09%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -734,14 +734,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -790,14 +790,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001014</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C18" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001180509886463268</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1014,14 +1014,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002135704384091754</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001105760034287844</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001083</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1259,21 +1259,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003622</v>
+        <v>0.001083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001061</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001917</v>
+        <v>0.003622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0004694</v>
+        <v>0.001061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1399,25 +1399,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.57</v>
+        <v>6.35</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0002168</v>
+        <v>0.001917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1427,25 +1427,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.5</v>
+        <v>5.03</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0004829</v>
+        <v>0.0004694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1455,25 +1455,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5.17</v>
+        <v>3.57</v>
       </c>
       <c r="C39" t="n">
-        <v>0.000678</v>
+        <v>0.0002168</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1483,25 +1483,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="C40" t="n">
-        <v>0.000203</v>
+        <v>0.0004829</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,25 +1511,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.21</v>
+        <v>5.17</v>
       </c>
       <c r="C41" t="n">
-        <v>0.001006</v>
+        <v>0.000678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1539,89 +1539,145 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5.21</v>
+        <v>5.29</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0001873</v>
+        <v>0.000203</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.001006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B46" t="n">
         <v>5.9</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C46" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-11 20:38</t>
+          <t>ultimo controllo: 2026-06-11 23:53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-13.38%</t>
+          <t>-17.55%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -678,14 +678,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -734,14 +734,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -790,14 +790,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -846,14 +846,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001014</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C19" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001180509886463268</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1042,14 +1042,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1070,14 +1070,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1126,14 +1126,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1182,14 +1182,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.002135704384091754</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1266,14 +1266,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0001105760034287844</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001083</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="C34" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.001083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.003622</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.39</v>
+        <v>4.25</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001061</v>
+        <v>0.003622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,25 +1399,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.35</v>
+        <v>3.39</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001917</v>
+        <v>0.001061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1427,25 +1427,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.03</v>
+        <v>6.35</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0004694</v>
+        <v>0.001917</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1455,25 +1455,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.57</v>
+        <v>5.03</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0002168</v>
+        <v>0.0004694</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1483,25 +1483,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0004829</v>
+        <v>0.0002168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,25 +1511,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5.17</v>
+        <v>3.5</v>
       </c>
       <c r="C41" t="n">
-        <v>0.000678</v>
+        <v>0.0004829</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1539,25 +1539,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000203</v>
+        <v>0.000678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1567,25 +1567,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.21</v>
+        <v>5.29</v>
       </c>
       <c r="C43" t="n">
-        <v>0.001006</v>
+        <v>0.000203</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1595,53 +1595,53 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5.21</v>
+        <v>4.21</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0001873</v>
+        <v>0.001006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>RPGKITTY</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4.53</v>
+        <v>5.21</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0001873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-28.51%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,33 +1651,61 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B47" t="n">
         <v>5.9</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C47" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-11 23:53</t>
+          <t>ultimo controllo: 2026-06-12 05:01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-17.55%</t>
+          <t>-18.40%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>21%</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-37.09%</t>
+          <t>-33.22%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -790,14 +790,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -846,14 +846,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -874,14 +874,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001014</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C21" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0001180509886463268</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1098,14 +1098,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002135704384091754</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1259,21 +1259,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0001105760034287844</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001083</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="C36" t="n">
-        <v>0.003622</v>
+        <v>0.001083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001061</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.35</v>
+        <v>4.25</v>
       </c>
       <c r="C38" t="n">
-        <v>0.001917</v>
+        <v>0.003622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1455,25 +1455,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5.03</v>
+        <v>3.39</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0004694</v>
+        <v>0.001061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1483,25 +1483,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.57</v>
+        <v>6.35</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0002168</v>
+        <v>0.001917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,25 +1511,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.5</v>
+        <v>5.03</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0004829</v>
+        <v>0.0004694</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1539,25 +1539,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5.17</v>
+        <v>3.57</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000678</v>
+        <v>0.0002168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1567,25 +1567,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5.29</v>
+        <v>3.5</v>
       </c>
       <c r="C43" t="n">
-        <v>0.000203</v>
+        <v>0.0004829</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1595,25 +1595,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.21</v>
+        <v>5.17</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001006</v>
+        <v>0.000678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1623,89 +1623,145 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOLDENGOAL</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5.21</v>
+        <v>5.29</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0001873</v>
+        <v>0.000203</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-28.34%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-05 20:55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>MONEY</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.001006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-88.80%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-05 16:08</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B49" t="n">
         <v>5.9</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C49" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-12 05:01</t>
+          <t>ultimo controllo: 2026-06-12 10:35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-33.22%</t>
+          <t>-32.13%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -930,14 +930,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001014</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0001180509886463268</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C25" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1259,21 +1259,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.002135704384091754</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0001105760034287844</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001083</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1427,21 +1427,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.003622</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1455,25 +1455,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001061</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1483,25 +1483,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6.35</v>
+        <v>4.45</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001917</v>
+        <v>0.001083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1511,25 +1511,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0004694</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1539,25 +1539,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.57</v>
+        <v>4.25</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0002168</v>
+        <v>0.003622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-20.16%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1567,25 +1567,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0004829</v>
+        <v>0.001061</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1595,25 +1595,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5.17</v>
+        <v>6.35</v>
       </c>
       <c r="C44" t="n">
-        <v>0.000678</v>
+        <v>0.001917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1623,25 +1623,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5.29</v>
+        <v>5.03</v>
       </c>
       <c r="C45" t="n">
-        <v>0.000203</v>
+        <v>0.0004694</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,25 +1651,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.21</v>
+        <v>3.57</v>
       </c>
       <c r="C46" t="n">
-        <v>0.001006</v>
+        <v>0.0002168</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1679,89 +1679,201 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5.21</v>
+        <v>3.5</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0001873</v>
+        <v>0.0004829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Bountywork</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4.53</v>
+        <v>5.17</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.000678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>+56.33%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-07 09:32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>GOLDENGOAL</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.000203</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-28.34%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>06-05 20:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MONEY</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.001006</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-88.80%</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>06-05 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Magpie</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0008541999999999999</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-35.09%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>06-03 20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>three</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B53" t="n">
         <v>5.9</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C53" t="n">
         <v>0.007389</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>-38.65%</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>06-03 20:08</t>
         </is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,50 +432,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_al_voto_USD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Eta_ore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Aggiornato_min_fa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Entrata_ipotetica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_dopo_3g</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>5.8</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>— nessun candidato sopra soglia —</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-12 10:35</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
+          <t>Velvet</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9458</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>liquidity_growth:2.88, coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.033</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>geckoterminal_trending</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0xbf927b841994731c573bdf09ceb0c6b0aa887cdd</t>
         </is>
       </c>
     </row>
@@ -487,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -499,29 +593,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -588,32 +682,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -622,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +877,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C15" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +933,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +961,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +989,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +1073,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1101,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1129,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0001014</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0001180509886463268</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1175,21 +1269,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1203,21 +1297,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1231,21 +1325,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1259,21 +1353,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C32" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1287,21 +1381,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1315,21 +1409,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1343,21 +1437,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1371,21 +1465,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,21 +1493,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.002135704384091754</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1427,21 +1521,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1455,21 +1549,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0001105760034287844</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1483,21 +1577,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001083</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1511,21 +1605,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1539,25 +1633,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.003622</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-20.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1567,25 +1661,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.001061</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1595,25 +1689,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001917</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1623,25 +1717,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0004694</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1651,25 +1745,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0002168</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1679,25 +1773,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0004829</v>
+        <v>0.001083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1707,25 +1801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.000678</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1735,25 +1829,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.29</v>
+        <v>4.25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.000203</v>
+        <v>0.003622</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>-20.16%</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1763,25 +1857,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4.21</v>
+        <v>3.39</v>
       </c>
       <c r="C50" t="n">
-        <v>0.001006</v>
+        <v>0.001061</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1791,91 +1885,231 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5.21</v>
+        <v>6.35</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0001873</v>
+        <v>0.001917</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.53</v>
+        <v>5.03</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0008541999999999999</v>
+        <v>0.0004694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-35.09%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-03 20:08</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>three</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5.9</v>
+        <v>3.57</v>
       </c>
       <c r="C53" t="n">
-        <v>0.007389</v>
+        <v>0.0002168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-38.65%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>06-07 16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BOUTYWORK</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0004829</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>-98.63%</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>06-07 14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Bountywork</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.000678</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>+56.33%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>06-07 09:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GOLDENGOAL</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.000203</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>-28.34%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>06-05 20:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MONEY</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.001006</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>-88.80%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>06-05 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RPGKITTY</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.0001873</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>-28.51%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>06-03 20:08</t>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>06-04 05:01</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.91</v>
+        <v>6.59</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9458</v>
+        <v>0.5188</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>liquidity_growth:2.88, coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.033</t>
+          <t>liquidity_growth:2.56, coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.028</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-18.40%</t>
+          <t>-25.93%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
@@ -668,11 +668,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-74.15%</t>
+          <t>-80.87%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -716,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00187842048057872</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C11" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.0001152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C12" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1.641e-05</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -856,14 +856,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.902e-05</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -884,14 +884,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9458</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -961,21 +961,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C19" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +1073,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1101,21 +1101,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1304,14 +1304,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1332,14 +1332,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0001014</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0001180509886463268</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C36" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1633,21 +1633,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.002135704384091754</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1717,21 +1717,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1745,21 +1745,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0001105760034287844</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.001083</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.003622</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-20.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1857,25 +1857,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.001061</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1885,25 +1885,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.35</v>
+        <v>4.45</v>
       </c>
       <c r="C51" t="n">
-        <v>0.001917</v>
+        <v>0.001083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1913,25 +1913,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0004694</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1941,25 +1941,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.57</v>
+        <v>4.25</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0002168</v>
+        <v>0.003622</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-20.16%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1969,25 +1969,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0004829</v>
+        <v>0.001061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1997,25 +1997,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bountywork</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5.17</v>
+        <v>6.35</v>
       </c>
       <c r="C55" t="n">
-        <v>0.000678</v>
+        <v>0.001917</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>+56.33%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2025,25 +2025,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-07 09:32</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GOLDENGOAL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5.29</v>
+        <v>5.03</v>
       </c>
       <c r="C56" t="n">
-        <v>0.000203</v>
+        <v>0.0004694</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-28.34%</t>
+          <t>-93.33%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2053,25 +2053,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-05 20:55</t>
+          <t>06-08 16:15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MONEY</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.21</v>
+        <v>3.57</v>
       </c>
       <c r="C57" t="n">
-        <v>0.001006</v>
+        <v>0.0002168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-88.80%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2081,35 +2081,35 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-05 16:08</t>
+          <t>06-07 16:42</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RPGKITTY</t>
+          <t>BOUTYWORK</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5.21</v>
+        <v>3.5</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0001873</v>
+        <v>0.0004829</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-28.51%</t>
+          <t>-98.63%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-04 05:01</t>
+          <t>06-07 14:17</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.59</v>
+        <v>6.13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5188</v>
+        <v>0.3938</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>liquidity_growth:2.56, coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.028</t>
+          <t>coingecko_trending:2.5, liquidity_growth:2.113, confluence_bonus:1.5, buy_pressure:0.022</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7.9</v>
+        <v>11.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-25.93%</t>
+          <t>+2864.89%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>22%</t>
         </is>
       </c>
     </row>
@@ -668,11 +668,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-80.87%</t>
+          <t>-73.58%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.13</v>
+        <v>5.96</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3938</v>
+        <v>0.4174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, liquidity_growth:2.113, confluence_bonus:1.5, buy_pressure:0.022</t>
+          <t>coingecko_trending:2.5, liquidity_growth:1.936, confluence_bonus:1.5, buy_pressure:0.019</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11.6</v>
+        <v>13.1</v>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-32.13%</t>
+          <t>-27.47%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
@@ -716,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001152</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>7.077e-05</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00187842048057872</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C14" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>0.0001152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -877,21 +877,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C15" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -940,14 +940,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.641e-05</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -968,14 +968,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.902e-05</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -996,14 +996,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9458</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +1073,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C22" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1101,21 +1101,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1136,14 +1136,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1297,21 +1297,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1388,14 +1388,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1416,14 +1416,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1444,14 +1444,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001014</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0001180509886463268</v>
+        <v>0.0001014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1633,21 +1633,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1717,21 +1717,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1745,21 +1745,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.002135704384091754</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0001105760034287844</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.001083</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1941,25 +1941,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.003622</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-20.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1969,25 +1969,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>XRPS</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.39</v>
+        <v>4.45</v>
       </c>
       <c r="C54" t="n">
-        <v>0.001061</v>
+        <v>0.001083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>+28.46%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1997,25 +1997,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-09 23:24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>AhwopB</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.001917</v>
+        <v>1.824027967974124e-05</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2025,25 +2025,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 14:57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>Jotchua</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5.03</v>
+        <v>4.25</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0004694</v>
+        <v>0.003622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-93.33%</t>
+          <t>-20.16%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2053,25 +2053,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-08 16:15</t>
+          <t>06-09 07:48</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.57</v>
+        <v>3.39</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0002168</v>
+        <v>0.001061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-07 16:42</t>
+          <t>06-09 04:21</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BOUTYWORK</t>
+          <t>GOKU</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.5</v>
+        <v>6.35</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0004829</v>
+        <v>0.001917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-98.63%</t>
+          <t>-16.45%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-07 14:17</t>
+          <t>06-08 19:33</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.96</v>
+        <v>5.31</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4174</v>
+        <v>0.4243</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, liquidity_growth:1.936, confluence_bonus:1.5, buy_pressure:0.019</t>
+          <t>coingecko_trending:2.5, confluence_bonus:1.5, liquidity_growth:1.303, buy_pressure:0.01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13.1</v>
+        <v>18.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -567,6 +567,53 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0xbf927b841994731c573bdf09ceb0c6b0aa887cdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SIREN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Siren Coin</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0007368</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.324, biz_mentions:0.113</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0xbCff5AF58099311135F183f1230F5F16BfaCF464</t>
         </is>
       </c>
     </row>
@@ -716,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +784,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +812,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.865e-05</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +840,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +868,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C13" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>0.0007368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,21 +896,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001152</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -877,21 +924,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7.077e-05</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +952,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00187842048057872</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -933,21 +980,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -961,21 +1008,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -989,21 +1036,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C19" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.0001152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1017,21 +1064,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C20" t="n">
-        <v>1.641e-05</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +1092,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.902e-05</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1080,14 +1127,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9458</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1101,21 +1148,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1129,21 +1176,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1204,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1232,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1260,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C27" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>0.9458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1288,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1316,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1297,21 +1344,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1325,21 +1372,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1353,21 +1400,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1381,21 +1428,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1409,21 +1456,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1437,21 +1484,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1465,21 +1512,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1493,21 +1540,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1528,14 +1575,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1549,21 +1596,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0001014</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1577,21 +1624,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1605,21 +1652,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1633,21 +1680,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0001180509886463268</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1661,21 +1708,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1689,21 +1736,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C44" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1717,21 +1764,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1745,21 +1792,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1773,21 +1820,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1801,21 +1848,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1829,21 +1876,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1857,21 +1904,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1885,21 +1932,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.002135704384091754</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1913,21 +1960,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1941,21 +1988,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0001105760034287844</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1969,25 +2016,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>XRPS</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.001083</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>+28.46%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1997,21 +2044,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-09 23:24</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AhwopB</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1.824027967974124e-05</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2025,25 +2072,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-09 14:57</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jotchua</t>
+          <t>2gtrGh</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003622</v>
+        <v>0.002135704384091754</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-20.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2053,25 +2100,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-09 07:48</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>2imoPS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.001061</v>
+        <v>2.187187606473225e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2081,25 +2128,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-09 04:21</t>
+          <t>06-10 08:13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GOKU</t>
+          <t>9ajKap</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.001917</v>
+        <v>0.0001105760034287844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2109,7 +2156,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-08 19:33</t>
+          <t>06-09 23:26</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.31</v>
+        <v>4.73</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4243</v>
+        <v>0.4021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, confluence_bonus:1.5, liquidity_growth:1.303, buy_pressure:0.01</t>
+          <t>coingecko_trending:2.5, confluence_bonus:1.5, liquidity_growth:0.729, buy_pressure:0.002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18.4</v>
+        <v>23.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.44</v>
+        <v>4.25</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007368</v>
+        <v>0.0007882</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.324, biz_mentions:0.113</t>
+          <t>coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.182, biz_mentions:0.063</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>150.6</v>
+        <v>155.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2864.89%</t>
+          <t>+2681.48%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
@@ -763,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.886e-05</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.823e-05</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -840,21 +840,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.791e-05</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -875,14 +875,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0007368</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C16" t="n">
-        <v>1.865e-05</v>
+        <v>0.0007368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -980,21 +980,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1008,21 +1008,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001152</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>7.077e-05</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1092,21 +1092,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00187842048057872</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C22" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>0.0001152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C23" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1211,14 +1211,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.641e-05</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1239,14 +1239,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.902e-05</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1267,14 +1267,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9458</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1344,21 +1344,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C30" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1372,21 +1372,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1407,14 +1407,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1659,14 +1659,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1687,14 +1687,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1715,14 +1715,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0001014</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1820,21 +1820,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0001180509886463268</v>
+        <v>0.0001014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1876,21 +1876,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1904,21 +1904,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>2HLTgk</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>3.221104091743028e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>AD9UmM</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>2.498187855578793e-06</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 13:07</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2gtrGh</t>
+          <t>uzuC8s</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.002135704384091754</v>
+        <v>8.508597307388731e-06</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2imoPS</t>
+          <t>Dd7LVW</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>2.187187606473225e-06</v>
+        <v>4.750710142372106e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-10 08:13</t>
+          <t>06-10 10:19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9ajKap</t>
+          <t>7m5R6G</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0001105760034287844</v>
+        <v>5.096719477676463e-06</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-09 23:26</t>
+          <t>06-10 08:42</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -444,7 +444,7 @@
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -525,27 +525,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Velvet</t>
+          <t>Siren Coin</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.73</v>
+        <v>4.14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4021</v>
+        <v>0.0007965</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, confluence_bonus:1.5, liquidity_growth:0.729, buy_pressure:0.002</t>
+          <t>coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.107, biz_mentions:0.037</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,64 +554,17 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>23.2</v>
+        <v>157.9</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>geckoterminal_trending</t>
+          <t>dexscreener_boosts</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>0xbf927b841994731c573bdf09ceb0c6b0aa887cdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SIREN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Siren Coin</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0007882</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.182, biz_mentions:0.063</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>155.4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>0xbCff5AF58099311135F183f1230F5F16BfaCF464</t>
         </is>
@@ -695,16 +648,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-27.47%</t>
+          <t>-28.12%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -763,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -812,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -840,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -868,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1.886e-05</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -896,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.823e-05</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -924,21 +877,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.791e-05</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -952,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0007368</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -980,21 +933,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1008,21 +961,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1036,21 +989,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.865e-05</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1064,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1092,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C21" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>0.0007368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1120,21 +1073,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0001152</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1148,21 +1101,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>7.077e-05</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1176,21 +1129,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00187842048057872</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1204,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1232,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1260,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C27" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.0001152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1288,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C28" t="n">
-        <v>1.641e-05</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1316,21 +1269,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.902e-05</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1351,14 +1304,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9458</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1372,21 +1325,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1400,21 +1353,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1428,21 +1381,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1456,21 +1409,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1484,21 +1437,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C35" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>0.9458</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1512,21 +1465,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1540,21 +1493,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1568,21 +1521,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1596,21 +1549,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1624,21 +1577,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1652,21 +1605,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1680,21 +1633,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1708,21 +1661,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1736,21 +1689,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1764,21 +1717,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1799,14 +1752,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1820,21 +1773,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0001014</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1848,21 +1801,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1876,21 +1829,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1904,21 +1857,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0001180509886463268</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1932,21 +1885,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1960,21 +1913,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>Hachi</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="C52" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>0.0001014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1988,21 +1941,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 04:51</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>HvxKHw</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>4.685100526239655e-06</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2016,21 +1969,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-10 22:18</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2HLTgk</t>
+          <t>CfHpp5</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>3.221104091743028e-06</v>
+        <v>6.533128867315285e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2044,21 +1997,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 20:46</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AD9UmM</t>
+          <t>9YVirA</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>2.498187855578793e-06</v>
+        <v>0.0001180509886463268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2072,21 +2025,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-10 13:07</t>
+          <t>06-10 18:50</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>uzuC8s</t>
+          <t>3PdqaN</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>8.508597307388731e-06</v>
+        <v>3.938116930369448e-06</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2100,21 +2053,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dd7LVW</t>
+          <t>3Pc75n</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>4.750710142372106e-06</v>
+        <v>2.753885728868227e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2128,21 +2081,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-10 10:19</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7m5R6G</t>
+          <t>3J9emJ</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>5.096719477676463e-06</v>
+        <v>2.310799235808331e-06</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2156,7 +2109,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-10 08:42</t>
+          <t>06-10 16:03</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.14</v>
+        <v>4.29</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007965</v>
+        <v>0.0007981</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, confluence_bonus:1.5, buy_pressure:0.107, biz_mentions:0.037</t>
+          <t>coingecko_trending:2.5, confluence_bonus:1.5, biz_mentions:0.25, buy_pressure:0.037</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>157.9</v>
+        <v>160.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>xboVjK</t>
+          <t>HYcP4h</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>6.95941896883086e-06</v>
+        <v>0.0001161892980484576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FQuDkt</t>
+          <t>3kQjTg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.499184263574482e-05</v>
+        <v>0.0001161856828380246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +765,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BnSiHL</t>
+          <t>5CGfdi</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000115408330626788</v>
+        <v>5.961818558830606e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7Nc9sr</t>
+          <t>AQyxFr</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.596e-05</v>
+        <v>2.810504873259007e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3Xf4nD</t>
+          <t>EpZZrR</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.023e-05</v>
+        <v>3.386440518902898e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>4mUhgP</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>0.02881504812803524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -877,21 +877,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C15" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>0.0001696</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 14:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -961,21 +961,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.886e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.823e-05</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.791e-05</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0007368</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +1073,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1101,21 +1101,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.865e-05</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0001152</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.49</v>
+        <v>4.44</v>
       </c>
       <c r="C28" t="n">
-        <v>7.077e-05</v>
+        <v>0.0007368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00187842048057872</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1297,21 +1297,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1.641e-05</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C34" t="n">
-        <v>1.902e-05</v>
+        <v>0.0001152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6.91</v>
+        <v>3.49</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9458</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1633,21 +1633,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C42" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1717,21 +1717,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1745,21 +1745,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hachi</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0001014</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1941,21 +1941,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-11 04:51</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HvxKHw</t>
+          <t>34iKvP</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>4.685100526239655e-06</v>
+        <v>9.097255240084683e-06</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-10 22:18</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CfHpp5</t>
+          <t>4hrPAB</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>6.533128867315285e-06</v>
+        <v>2.758171440316367e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-10 20:46</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9YVirA</t>
+          <t>8YBVUb</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0001180509886463268</v>
+        <v>7.083865756646603e-07</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-10 18:50</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3PdqaN</t>
+          <t>754E9M</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>3.938116930369448e-06</v>
+        <v>6.921126755487895e-06</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3Pc75n</t>
+          <t>CHSsGh</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>2.753885728868227e-06</v>
+        <v>2.759550450931508e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3J9emJ</t>
+          <t>DorgBp</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>2.310799235808331e-06</v>
+        <v>1.908359005798709e-06</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-10 16:03</t>
+          <t>06-11 11:00</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,20 +432,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
@@ -525,39 +525,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Siren Coin</t>
+          <t>It's called Soccer</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.29</v>
+        <v>4.54</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007981</v>
+        <v>0.0001284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>coingecko_trending:2.5, confluence_bonus:1.5, biz_mentions:0.25, buy_pressure:0.037</t>
+          <t>volume_accel:1.722, confluence_bonus:1.5, young_with_volume:1.291, buy_pressure:0.028</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>solana</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>160.2</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -566,7 +566,54 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0xbCff5AF58099311135F183f1230F5F16BfaCF464</t>
+          <t>FFosggieyf6ceEdapfQjeWetyFr9CjUzm9BLoxbopump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TRILLIONAIRE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trillionaire</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.53e-05</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.291</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dexscreener_boosts</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0x37E1f000acF0eF4593e75A2c667f09dC93ce1110</t>
         </is>
       </c>
     </row>
@@ -628,16 +675,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2681.48%</t>
+          <t>+2590.42%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23%</t>
         </is>
       </c>
     </row>
@@ -716,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HYcP4h</t>
+          <t>52yHY5</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001161892980484576</v>
+        <v>2.288650613446281e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +784,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3kQjTg</t>
+          <t>Fzu6LR</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001161856828380246</v>
+        <v>8.552470253231173e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +812,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5CGfdi</t>
+          <t>9R9kr1</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5.961818558830606e-06</v>
+        <v>0.0001159646553349961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +840,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AQyxFr</t>
+          <t>GEy2Ky</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.810504873259007e-06</v>
+        <v>9.959724800374615e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -821,21 +868,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EpZZrR</t>
+          <t>DLoqKa</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3.386440518902898e-05</v>
+        <v>3.237422903124358e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -849,21 +896,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4mUhgP</t>
+          <t>3LqVF6</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02881504812803524</v>
+        <v>0.000145183637842064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -877,21 +924,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOCCER</t>
+          <t>HYcP4h</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001696</v>
+        <v>0.0001161892980484576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +952,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-13 14:20</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>xboVjK</t>
+          <t>3kQjTg</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>6.95941896883086e-06</v>
+        <v>0.0001161856828380246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -933,21 +980,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FQuDkt</t>
+          <t>5CGfdi</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.499184263574482e-05</v>
+        <v>5.961818558830606e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -961,21 +1008,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BnSiHL</t>
+          <t>AQyxFr</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000115408330626788</v>
+        <v>2.810504873259007e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -989,21 +1036,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7Nc9sr</t>
+          <t>EpZZrR</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.596e-05</v>
+        <v>3.386440518902898e-05</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1017,21 +1064,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3Xf4nD</t>
+          <t>4mUhgP</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2.023e-05</v>
+        <v>0.02881504812803524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +1092,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C21" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>0.0001696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +1120,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 14:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1101,21 +1148,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1129,21 +1176,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1157,21 +1204,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.886e-05</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1185,21 +1232,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.823e-05</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1260,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.791e-05</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1288,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0007368</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1316,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1297,21 +1344,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1325,21 +1372,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1.865e-05</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1353,21 +1400,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1381,21 +1428,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1409,21 +1456,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.48</v>
+        <v>4.44</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0001152</v>
+        <v>0.0007368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1437,21 +1484,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>7.077e-05</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1465,21 +1512,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00187842048057872</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1493,21 +1540,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1521,21 +1568,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1549,21 +1596,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1577,21 +1624,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C40" t="n">
-        <v>1.641e-05</v>
+        <v>0.0001152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1605,21 +1652,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C41" t="n">
-        <v>1.902e-05</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1633,21 +1680,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9458</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1661,21 +1708,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1689,21 +1736,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1717,21 +1764,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1745,21 +1792,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1773,21 +1820,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1801,21 +1848,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C48" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>0.9458</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1829,21 +1876,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1857,21 +1904,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1885,21 +1932,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1913,21 +1960,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1941,21 +1988,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>34iKvP</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>9.097255240084683e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1969,21 +2016,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4hrPAB</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2.758171440316367e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1997,21 +2044,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8YBVUb</t>
+          <t>BASk9P</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>7.083865756646603e-07</v>
+        <v>8.834440920160441e-06</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2025,21 +2072,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 23:53</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>754E9M</t>
+          <t>WRXxav</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>6.921126755487895e-06</v>
+        <v>3.956226680374402e-08</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2053,21 +2100,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHSsGh</t>
+          <t>8aykK8</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>2.759550450931508e-06</v>
+        <v>3.325031999033651e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2081,21 +2128,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-11 20:38</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DorgBp</t>
+          <t>339hgL</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1.908359005798709e-06</v>
+        <v>7.854945794194488e-06</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2109,7 +2156,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-11 11:00</t>
+          <t>06-11 16:23</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -525,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,14 +538,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.54</v>
+        <v>4.25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001284</v>
+        <v>0.000147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.722, confluence_bonus:1.5, young_with_volume:1.291, buy_pressure:0.028</t>
+          <t>volume_accel:1.544, confluence_bonus:1.5, young_with_volume:1.158, buy_pressure:0.048</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -588,11 +588,11 @@
         <v>4.04</v>
       </c>
       <c r="E3" t="n">
-        <v>2.53e-05</v>
+        <v>2.266e-05</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.291</t>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.286</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>36.9</v>
+        <v>39</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2590.42%</t>
+          <t>+2424.93%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>22%</t>
         </is>
       </c>
     </row>
@@ -763,14 +763,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>52yHY5</t>
+          <t>45fmRc</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.288650613446281e-06</v>
+        <v>1.44021765671264e-06</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fzu6LR</t>
+          <t>4vmBJS</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8.552470253231173e-06</v>
+        <v>4.456830839620417e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9R9kr1</t>
+          <t>Dpei2b</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001159646553349961</v>
+        <v>1.277e-05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -840,21 +840,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GEy2Ky</t>
+          <t>BTVASD</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.959724800374615e-06</v>
+        <v>2.02e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -868,21 +868,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DLoqKa</t>
+          <t>52yHY5</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3.237422903124358e-06</v>
+        <v>2.288650613446281e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -903,14 +903,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3LqVF6</t>
+          <t>Fzu6LR</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000145183637842064</v>
+        <v>8.552470253231173e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -931,14 +931,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HYcP4h</t>
+          <t>9R9kr1</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001161892980484576</v>
+        <v>0.0001159646553349961</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3kQjTg</t>
+          <t>GEy2Ky</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001161856828380246</v>
+        <v>9.959724800374615e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -980,21 +980,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5CGfdi</t>
+          <t>DLoqKa</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>5.961818558830606e-06</v>
+        <v>3.237422903124358e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1008,21 +1008,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AQyxFr</t>
+          <t>3LqVF6</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.810504873259007e-06</v>
+        <v>0.000145183637842064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EpZZrR</t>
+          <t>HYcP4h</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3.386440518902898e-05</v>
+        <v>0.0001161892980484576</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1071,14 +1071,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4mUhgP</t>
+          <t>3kQjTg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02881504812803524</v>
+        <v>0.0001161856828380246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1099,14 +1099,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOCCER</t>
+          <t>5CGfdi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001696</v>
+        <v>5.961818558830606e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-13 14:20</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xboVjK</t>
+          <t>AQyxFr</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>6.95941896883086e-06</v>
+        <v>2.810504873259007e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FQuDkt</t>
+          <t>EpZZrR</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.499184263574482e-05</v>
+        <v>3.386440518902898e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BnSiHL</t>
+          <t>4mUhgP</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.000115408330626788</v>
+        <v>0.02881504812803524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1204,21 +1204,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7Nc9sr</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C25" t="n">
-        <v>1.596e-05</v>
+        <v>0.0001696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1232,21 +1232,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3Xf4nD</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>2.023e-05</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1267,14 +1267,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1344,21 +1344,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1372,21 +1372,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1.886e-05</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1.823e-05</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1.791e-05</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1456,21 +1456,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0007368</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1.865e-05</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C38" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>0.0007368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0001152</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>7.077e-05</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1680,21 +1680,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.00187842048057872</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C44" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.0001152</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C45" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1.641e-05</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1827,14 +1827,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>1.902e-05</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1855,14 +1855,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9458</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1876,21 +1876,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1904,21 +1904,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C52" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BASk9P</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8.834440920160441e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-11 23:53</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WRXxav</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>3.956226680374402e-08</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8aykK8</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>3.325031999033651e-06</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-11 20:38</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>339hgL</t>
+          <t>6tegL9</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>7.854945794194488e-06</v>
+        <v>1.196949104652351e-05</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-11 16:23</t>
+          <t>06-12 05:01</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -432,12 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -445,7 +445,7 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
@@ -525,39 +525,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SOCCER</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>It's called Soccer</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000147</v>
+        <v>2.801e-05</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>volume_accel:1.544, confluence_bonus:1.5, young_with_volume:1.158, buy_pressure:0.048</t>
+          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>solana</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>40.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -565,53 +565,6 @@
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>FFosggieyf6ceEdapfQjeWetyFr9CjUzm9BLoxbopump</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TRILLIONAIRE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Trillionaire</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.266e-05</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.286</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>39</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>0x37E1f000acF0eF4593e75A2c667f09dC93ce1110</t>
         </is>
@@ -763,14 +716,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>45fmRc</t>
+          <t>EWGXrq</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.44021765671264e-06</v>
+        <v>0.001889273515688411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -784,21 +737,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-13 21:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4vmBJS</t>
+          <t>45fmRc</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4.456830839620417e-06</v>
+        <v>1.44021765671264e-06</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -819,14 +772,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dpei2b</t>
+          <t>4vmBJS</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.277e-05</v>
+        <v>4.456830839620417e-06</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -847,14 +800,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTVASD</t>
+          <t>Dpei2b</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.02e-05</v>
+        <v>1.277e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -875,14 +828,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>52yHY5</t>
+          <t>BTVASD</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.288650613446281e-06</v>
+        <v>2.02e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -896,21 +849,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fzu6LR</t>
+          <t>52yHY5</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>8.552470253231173e-06</v>
+        <v>2.288650613446281e-06</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -931,14 +884,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9R9kr1</t>
+          <t>Fzu6LR</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001159646553349961</v>
+        <v>8.552470253231173e-06</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -959,14 +912,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GEy2Ky</t>
+          <t>9R9kr1</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>9.959724800374615e-06</v>
+        <v>0.0001159646553349961</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -987,14 +940,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DLoqKa</t>
+          <t>GEy2Ky</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3.237422903124358e-06</v>
+        <v>9.959724800374615e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1015,14 +968,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3LqVF6</t>
+          <t>DLoqKa</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000145183637842064</v>
+        <v>3.237422903124358e-06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1043,14 +996,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HYcP4h</t>
+          <t>3LqVF6</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001161892980484576</v>
+        <v>0.000145183637842064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1064,21 +1017,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3kQjTg</t>
+          <t>HYcP4h</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001161856828380246</v>
+        <v>0.0001161892980484576</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1099,14 +1052,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5CGfdi</t>
+          <t>3kQjTg</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>5.961818558830606e-06</v>
+        <v>0.0001161856828380246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1127,14 +1080,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AQyxFr</t>
+          <t>5CGfdi</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.810504873259007e-06</v>
+        <v>5.961818558830606e-06</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1155,14 +1108,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EpZZrR</t>
+          <t>AQyxFr</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>3.386440518902898e-05</v>
+        <v>2.810504873259007e-06</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1183,14 +1136,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4mUhgP</t>
+          <t>EpZZrR</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02881504812803524</v>
+        <v>3.386440518902898e-05</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1211,14 +1164,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOCCER</t>
+          <t>4mUhgP</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0001696</v>
+        <v>0.02881504812803524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1232,21 +1185,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-13 14:20</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xboVjK</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C26" t="n">
-        <v>6.95941896883086e-06</v>
+        <v>0.0001696</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1260,21 +1213,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FQuDkt</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.499184263574482e-05</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1295,14 +1248,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BnSiHL</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.000115408330626788</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1323,14 +1276,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7Nc9sr</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.596e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1351,14 +1304,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3Xf4nD</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2.023e-05</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1379,14 +1332,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1400,21 +1353,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1435,14 +1388,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1463,14 +1416,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1484,21 +1437,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1.886e-05</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1519,14 +1472,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1.823e-05</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1547,14 +1500,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1.791e-05</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1575,14 +1528,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0007368</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1596,21 +1549,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C39" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>0.0007368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1624,21 +1577,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1659,14 +1612,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1.865e-05</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1687,14 +1640,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1708,21 +1661,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1743,14 +1696,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0001152</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1764,21 +1717,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="C45" t="n">
-        <v>7.077e-05</v>
+        <v>0.0001152</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1799,14 +1752,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00187842048057872</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1820,21 +1773,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1855,14 +1808,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1911,14 +1864,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>1.641e-05</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1939,14 +1892,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1.902e-05</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1967,14 +1920,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9458</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1988,21 +1941,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C53" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2016,21 +1969,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2051,14 +2004,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2079,14 +2032,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2107,14 +2060,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>5BuMZJ</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.599479169558045e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2128,21 +2081,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6tegL9</t>
+          <t>CDgBhK</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1.196949104652351e-05</v>
+        <v>9.318408086212118e-05</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -27,12 +27,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,141 +429,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Score_su_10</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score_grezzo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_al_voto_USD</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Perche_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Eta_ore</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aggiornato_min_fa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Entrata_ipotetica</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_dopo_3g</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Esito</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>— nessun candidato sopra soglia —</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.801e-05</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>biz_mentions:1.5, confluence_bonus:1.5, telegram_velocity:0.75, buy_pressure:0.25</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dexscreener_boosts</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0x37E1f000acF0eF4593e75A2c667f09dC93ce1110</t>
+          <t>ultimo controllo: 2026-06-13 23:23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>il sistema sta osservando; nessuna confluenza forte ora</t>
         </is>
       </c>
     </row>
@@ -593,29 +499,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>VALIDAZIONE — gli score alti si muovono DAVVERO? (rendimento NETTO di slippage+fee)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Orizzonte</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Valore atteso NETTO</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Win rate</t>
         </is>
@@ -682,32 +588,32 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Score_entry</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Prezzo_entry</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ret_72h_netto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Entrata</t>
         </is>
@@ -716,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EWGXrq</t>
+          <t>PAsbPA</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001889273515688411</v>
+        <v>1.419733333333333e-05</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 21:31</t>
+          <t>06-13 23:23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>45fmRc</t>
+          <t>DX8sgC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.44021765671264e-06</v>
+        <v>2.192e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -765,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-13 23:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4vmBJS</t>
+          <t>EWGXrq</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4.456830839620417e-06</v>
+        <v>0.001889273515688411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -793,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-13 21:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dpei2b</t>
+          <t>45fmRc</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.277e-05</v>
+        <v>1.44021765671264e-06</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -828,14 +734,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTVASD</t>
+          <t>4vmBJS</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.02e-05</v>
+        <v>4.456830839620417e-06</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -856,14 +762,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52yHY5</t>
+          <t>Dpei2b</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.288650613446281e-06</v>
+        <v>1.277e-05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -877,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fzu6LR</t>
+          <t>BTVASD</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>8.552470253231173e-06</v>
+        <v>2.02e-05</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -905,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9R9kr1</t>
+          <t>52yHY5</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001159646553349961</v>
+        <v>2.288650613446281e-06</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -940,14 +846,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GEy2Ky</t>
+          <t>Fzu6LR</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>9.959724800374615e-06</v>
+        <v>8.552470253231173e-06</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -968,14 +874,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DLoqKa</t>
+          <t>9R9kr1</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3.237422903124358e-06</v>
+        <v>0.0001159646553349961</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -996,14 +902,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3LqVF6</t>
+          <t>GEy2Ky</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000145183637842064</v>
+        <v>9.959724800374615e-06</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1024,14 +930,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HYcP4h</t>
+          <t>DLoqKa</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001161892980484576</v>
+        <v>3.237422903124358e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1045,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3kQjTg</t>
+          <t>3LqVF6</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001161856828380246</v>
+        <v>0.000145183637842064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1073,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5CGfdi</t>
+          <t>HYcP4h</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>5.961818558830606e-06</v>
+        <v>0.0001161892980484576</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1108,14 +1014,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AQyxFr</t>
+          <t>3kQjTg</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.810504873259007e-06</v>
+        <v>0.0001161856828380246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1136,14 +1042,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EpZZrR</t>
+          <t>5CGfdi</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3.386440518902898e-05</v>
+        <v>5.961818558830606e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1164,14 +1070,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4mUhgP</t>
+          <t>AQyxFr</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02881504812803524</v>
+        <v>2.810504873259007e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1192,14 +1098,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOCCER</t>
+          <t>EpZZrR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0001696</v>
+        <v>3.386440518902898e-05</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1213,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-13 14:20</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>xboVjK</t>
+          <t>4mUhgP</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>6.95941896883086e-06</v>
+        <v>0.02881504812803524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1241,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FQuDkt</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C28" t="n">
-        <v>1.499184263574482e-05</v>
+        <v>0.0001696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1269,21 +1175,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BnSiHL</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000115408330626788</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1304,14 +1210,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7Nc9sr</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1.596e-05</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1332,14 +1238,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3Xf4nD</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2.023e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1360,14 +1266,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1381,21 +1287,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1409,21 +1315,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1444,14 +1350,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1465,21 +1371,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1.886e-05</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1493,21 +1399,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1.823e-05</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1528,14 +1434,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1.791e-05</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1556,14 +1462,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0007368</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1577,21 +1483,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1605,21 +1511,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C41" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>0.0007368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1633,21 +1539,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>1.865e-05</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1668,14 +1574,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1689,21 +1595,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1717,21 +1623,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0001152</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1745,21 +1651,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>7.077e-05</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1773,21 +1679,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00187842048057872</v>
+        <v>0.0001152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1801,21 +1707,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C48" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1829,21 +1735,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1864,14 +1770,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1892,14 +1798,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1.641e-05</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1920,14 +1826,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>EX7jHJ</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>1.902e-05</v>
+        <v>8.246880963566606e-06</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1948,14 +1854,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>A3MA7J</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9458</v>
+        <v>1.641e-05</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1969,21 +1875,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>5NKa4G</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>1.902e-05</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1997,21 +1903,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="C55" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>0.9458</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2025,21 +1931,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:34</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>Cg6nCx</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>2.602131251274632e-06</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2060,14 +1966,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5BuMZJ</t>
+          <t>BqMz2a</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>2.599479169558045e-06</v>
+        <v>2.600575521017427e-06</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2088,14 +1994,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CDgBhK</t>
+          <t>xtbBZ8</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>9.318408086212118e-05</v>
+        <v>2.600218389817967e-06</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2109,7 +2015,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-12 05:01</t>
+          <t>06-12 10:34</t>
         </is>
       </c>
     </row>

--- a/top_scores.xlsx
+++ b/top_scores.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ultimo controllo: 2026-06-13 23:23</t>
+          <t>ultimo controllo: 2026-06-14 05:07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2424.93%</t>
+          <t>+2284.28%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-28.12%</t>
+          <t>-32.91%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAsbPA</t>
+          <t>FvjBUN</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.419733333333333e-05</v>
+        <v>4.544660869327245e-05</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -643,21 +643,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06-13 23:23</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DX8sgC</t>
+          <t>GdxM9U</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.192e-05</v>
+        <v>2.428593198860585e-05</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -671,21 +671,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06-13 23:23</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EWGXrq</t>
+          <t>7YxRTV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001889273515688411</v>
+        <v>4.33162453901945e-05</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -699,21 +699,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06-13 21:31</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>45fmRc</t>
+          <t>bsj9cE</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.44021765671264e-06</v>
+        <v>1.623e-05</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -727,21 +727,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4vmBJS</t>
+          <t>FeYVh9</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>4.456830839620417e-06</v>
+        <v>2.31e-05</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -755,21 +755,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dpei2b</t>
+          <t>FH4sGN</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.277e-05</v>
+        <v>1.802e-05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BTVASD</t>
+          <t>E2c2sK</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2.02e-05</v>
+        <v>1.743e-05</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06-13 19:54</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52yHY5</t>
+          <t>6toXkH</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.288650613446281e-06</v>
+        <v>1.974e-05</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -839,21 +839,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-14 05:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fzu6LR</t>
+          <t>PAsbPA</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>8.552470253231173e-06</v>
+        <v>1.419733333333333e-05</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -867,21 +867,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 23:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9R9kr1</t>
+          <t>DX8sgC</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001159646553349961</v>
+        <v>2.192e-05</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 23:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GEy2Ky</t>
+          <t>EWGXrq</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>9.959724800374615e-06</v>
+        <v>0.001889273515688411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 21:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DLoqKa</t>
+          <t>45fmRc</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3.237422903124358e-06</v>
+        <v>1.44021765671264e-06</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3LqVF6</t>
+          <t>4vmBJS</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.000145183637842064</v>
+        <v>4.456830839620417e-06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06-13 17:46</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HYcP4h</t>
+          <t>Dpei2b</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0001161892980484576</v>
+        <v>1.277e-05</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3kQjTg</t>
+          <t>BTVASD</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001161856828380246</v>
+        <v>2.02e-05</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1035,21 +1035,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 19:54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5CGfdi</t>
+          <t>52yHY5</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>5.961818558830606e-06</v>
+        <v>2.288650613446281e-06</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AQyxFr</t>
+          <t>Fzu6LR</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.810504873259007e-06</v>
+        <v>8.552470253231173e-06</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EpZZrR</t>
+          <t>9R9kr1</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3.386440518902898e-05</v>
+        <v>0.0001159646553349961</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4mUhgP</t>
+          <t>GEy2Ky</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02881504812803524</v>
+        <v>9.959724800374615e-06</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>06-13 14:25</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SOCCER</t>
+          <t>DLoqKa</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0001696</v>
+        <v>3.237422903124358e-06</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06-13 14:20</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>xboVjK</t>
+          <t>3LqVF6</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>6.95941896883086e-06</v>
+        <v>0.000145183637842064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1203,21 +1203,21 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 17:46</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FQuDkt</t>
+          <t>HYcP4h</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1.499184263574482e-05</v>
+        <v>0.0001161892980484576</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BnSiHL</t>
+          <t>3kQjTg</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.000115408330626788</v>
+        <v>0.0001161856828380246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1259,21 +1259,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7Nc9sr</t>
+          <t>5CGfdi</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1.596e-05</v>
+        <v>5.961818558830606e-06</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3Xf4nD</t>
+          <t>AQyxFr</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.023e-05</v>
+        <v>2.810504873259007e-06</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1315,21 +1315,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>06-13 12:06</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6zP8q2</t>
+          <t>EpZZrR</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.233354995855494e-06</v>
+        <v>3.386440518902898e-05</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5d1RMc</t>
+          <t>4mUhgP</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2.302845840003346e-05</v>
+        <v>0.02881504812803524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 14:25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12BnNN</t>
+          <t>SOCCER</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C36" t="n">
-        <v>2.533316397337921e-05</v>
+        <v>0.0001696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06-13 09:37</t>
+          <t>06-13 14:20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>83UMxv</t>
+          <t>xboVjK</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1.779645829494278e-05</v>
+        <v>6.95941896883086e-06</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1427,21 +1427,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CCpPzP</t>
+          <t>FQuDkt</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1.886e-05</v>
+        <v>1.499184263574482e-05</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BeHYx3</t>
+          <t>BnSiHL</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1.823e-05</v>
+        <v>0.000115408330626788</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BJ6CdX</t>
+          <t>7Nc9sr</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>1.791e-05</v>
+        <v>1.596e-05</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06-13 04:49</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SIREN</t>
+          <t>3Xf4nD</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0007368</v>
+        <v>2.023e-05</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06-13 04:42</t>
+          <t>06-13 12:06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DxeNVt</t>
+          <t>6zP8q2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.782843553848796e-06</v>
+        <v>2.233354995855494e-06</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B8e6vF</t>
+          <t>5d1RMc</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>7.988257434136125e-05</v>
+        <v>2.302845840003346e-05</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CyNkMF</t>
+          <t>12BnNN</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1.865e-05</v>
+        <v>2.533316397337921e-05</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1623,21 +1623,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06-12 23:34</t>
+          <t>06-13 09:37</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7wmBXW</t>
+          <t>83UMxv</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>2.501937374426156e-06</v>
+        <v>1.779645829494278e-05</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FWJiin</t>
+          <t>CCpPzP</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>2.509218508266756e-06</v>
+        <v>1.886e-05</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06-12 18:21</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Trillionaire</t>
+          <t>BeHYx3</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0001152</v>
+        <v>1.823e-05</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TRILLIONAIRE</t>
+          <t>BJ6CdX</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>7.077e-05</v>
+        <v>1.791e-05</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1735,21 +1735,21 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06-12 18:14</t>
+          <t>06-13 04:49</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HnXZeB</t>
+          <t>SIREN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00187842048057872</v>
+        <v>0.0007368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-13 04:42</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9QQ9eT</t>
+          <t>DxeNVt</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.586509071096071e-06</v>
+        <v>2.782843553848796e-06</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1791,21 +1791,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>B8e6vF</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>7.988257434136125e-05</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EX7jHJ</t>
+          <t>CyNkMF</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>8.246880963566606e-06</v>
+        <v>1.865e-05</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 23:34</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A3MA7J</t>
+          <t>7wmBXW</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1.641e-05</v>
+        <v>2.501937374426156e-06</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1875,21 +1875,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5NKa4G</t>
+          <t>FWJiin</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>1.902e-05</v>
+        <v>2.509218508266756e-06</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06-12 15:41</t>
+          <t>06-12 18:21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>Trillionaire</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.91</v>
+        <v>3.48</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9458</v>
+        <v>0.0001152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06-12 15:34</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cg6nCx</t>
+          <t>TRILLIONAIRE</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="C56" t="n">
-        <v>2.602131251274632e-06</v>
+        <v>7.077e-05</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 18:14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BqMz2a</t>
+          <t>HnXZeB</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>2.600575521017427e-06</v>
+        <v>0.00187842048057872</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>xtbBZ8</t>
+          <t>9QQ9eT</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>2.600218389817967e-06</v>
+        <v>8.586509071096071e-06</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>06-12 10:34</t>
+          <t>06-12 15:41</t>
         </is>
       </c>
     </row>
